--- a/resources/design_documents/BOM-thermal-loop.xlsx
+++ b/resources/design_documents/BOM-thermal-loop.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\github\thermal-loop\resources\design_documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/94ce74fd9ae883e9/Documents/GitHub/thermal-loop/resources/design_documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80E5F55D-10A6-42B5-AE9E-C0AB2EBC7ED2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="13_ncr:1_{80E5F55D-10A6-42B5-AE9E-C0AB2EBC7ED2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E9AC8987-F238-4932-88EE-4BEB160FD40B}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-150" windowWidth="29040" windowHeight="15840" xr2:uid="{FDAE7DA4-9528-4FC7-A320-70DA50473DCE}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{FDAE7DA4-9528-4FC7-A320-70DA50473DCE}"/>
   </bookViews>
   <sheets>
     <sheet name="bill_of_materials" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
   <si>
     <t>Total Cost</t>
   </si>
@@ -77,12 +77,6 @@
     <t xml:space="preserve">Notes </t>
   </si>
   <si>
-    <t>https://www.grainger.com/product/4WPU6?gucid=N:N:PS:Paid:GGL:CSM-2295:39CUA3:20800606:APZ_1&amp;gclsrc=aw.ds&amp;gad_source=1&amp;gad_campaignid=22475796619&amp;gclid=CjwKCAiA3-3KBhBiEiwA2x7FdKUdLy5CUHWAWkzf3kiPh_wTUjzerfnVLuy6BLzuXajRBG0WmBupKhoCW9kQAvD_BwE</t>
-  </si>
-  <si>
-    <t>Pipe Flange: Floor Flange, 304 Stainless Steel, 1/2 in Pipe Size, 3 1/2 in Flange Outside Dia</t>
-  </si>
-  <si>
     <t>https://www.grainger.com/product/1MKB7?gucid=N:N:PS:Paid:GGL:CSM-2295:ZRUQJH:20800606:APZ_1&amp;gclsrc=aw.ds&amp;gad_source=4&amp;gad_campaignid=22472343581&amp;gclid=CjwKCAiA3-3KBhBiEiwA2x7FdMbC-r7MRiVr7w70QY_m83YfUZOkHFETUemE48AeCoPwtwXNXI1CgxoCD1UQAvD_BwE</t>
   </si>
   <si>
@@ -105,6 +99,21 @@
   </si>
   <si>
     <t>R83118-36 | NICHROME ROD .125 OD X 36" L | Crown Engineering</t>
+  </si>
+  <si>
+    <t>Pipe Flange: Floor Flange, 304 Stainless Steel, 1 in Pipe Size, 4 1/4 in Flange Outside Diameter</t>
+  </si>
+  <si>
+    <t>Needed Larger Flange, but can downsize if needed</t>
+  </si>
+  <si>
+    <t>https://www.grainger.com/product/Pipe-Flange-Floor-Flange-4WPU8</t>
+  </si>
+  <si>
+    <t>PARKER Compression Fitting Adapter: 3/8 in OD x 1/2 in Pipe Fitting Size, Compression x MNPT</t>
+  </si>
+  <si>
+    <t>https://www.grainger.com/product/1PZD5?gucid=N:N:FPL:Free:MS:CSM-1946:tew63h4:20501231&amp;gucid=N:N:PS:Paid:GGL:CSM-2295:UU5CX9:20800606:APZ_1&amp;gclsrc=aw.ds&amp;gad_source=1&amp;gad_campaignid=22475795893&amp;gclid=Cj0KCQiAgvPKBhCxARIsAOlK_EpGTxCUrLLeHl2B2PDU9Qyz8Ndfo0lyhe-JfENwhXPI-CsP3xbN6h8aAu77EALw_wcB</t>
   </si>
 </sst>
 </file>
@@ -512,22 +521,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6D3A36C-E8CE-4E50-A172-E48E2F9A45A8}">
   <dimension ref="A1:L43"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="25.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="25.44140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="74" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="12.28515625" customWidth="1"/>
-    <col min="7" max="7" width="69.42578125" customWidth="1"/>
+    <col min="3" max="3" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="12.33203125" customWidth="1"/>
+    <col min="7" max="7" width="69.44140625" customWidth="1"/>
     <col min="8" max="8" width="76" customWidth="1"/>
-    <col min="9" max="9" width="83.5703125" customWidth="1"/>
-    <col min="10" max="10" width="62.5703125" customWidth="1"/>
-    <col min="11" max="11" width="55.85546875" customWidth="1"/>
+    <col min="9" max="9" width="83.5546875" customWidth="1"/>
+    <col min="10" max="10" width="62.5546875" customWidth="1"/>
+    <col min="11" max="11" width="55.88671875" customWidth="1"/>
     <col min="12" max="12" width="51" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>1</v>
       </c>
@@ -565,36 +574,38 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="C2" s="2">
         <v>1</v>
       </c>
       <c r="D2" s="6">
-        <v>42.1</v>
+        <v>61.71</v>
       </c>
       <c r="E2" s="6">
         <f>C2*D2</f>
-        <v>42.1</v>
-      </c>
-      <c r="F2" s="6"/>
+        <v>61.71</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>22</v>
+      </c>
       <c r="G2" s="3" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="H2" s="4"/>
       <c r="I2" s="4"/>
     </row>
-    <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C3" s="2">
         <v>1</v>
@@ -608,32 +619,40 @@
       </c>
       <c r="F3" s="6"/>
       <c r="G3" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H3" s="4"/>
     </row>
-    <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="6"/>
+        <v>17</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" s="2">
+        <v>1</v>
+      </c>
+      <c r="D4" s="6">
+        <v>47.2</v>
+      </c>
       <c r="E4" s="6">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>47.2</v>
       </c>
       <c r="F4" s="6"/>
-      <c r="G4" s="3"/>
+      <c r="G4" s="3" t="s">
+        <v>25</v>
+      </c>
       <c r="H4" s="5"/>
       <c r="I4" s="5"/>
     </row>
-    <row r="5" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" s="6"/>
@@ -643,12 +662,12 @@
       </c>
       <c r="F5" s="6"/>
       <c r="G5" s="3" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="H5" s="3"/>
       <c r="I5" s="2"/>
     </row>
-    <row r="6" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
@@ -662,7 +681,7 @@
       <c r="H6" s="3"/>
       <c r="I6" s="3"/>
     </row>
-    <row r="7" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
@@ -676,7 +695,7 @@
       <c r="H7" s="3"/>
       <c r="I7" s="2"/>
     </row>
-    <row r="8" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
@@ -688,7 +707,7 @@
       <c r="F8" s="6"/>
       <c r="G8" s="3"/>
     </row>
-    <row r="9" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
@@ -702,7 +721,7 @@
       <c r="H9" s="5"/>
       <c r="I9" s="5"/>
     </row>
-    <row r="10" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
@@ -716,7 +735,7 @@
       <c r="H10" s="3"/>
       <c r="I10" s="5"/>
     </row>
-    <row r="11" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
@@ -729,7 +748,7 @@
       <c r="G11" s="3"/>
       <c r="H11" s="5"/>
     </row>
-    <row r="12" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="2"/>
       <c r="B12" s="5"/>
       <c r="C12" s="2"/>
@@ -742,7 +761,7 @@
       <c r="G12" s="3"/>
       <c r="H12" s="5"/>
     </row>
-    <row r="13" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
@@ -754,7 +773,7 @@
       <c r="F13" s="6"/>
       <c r="G13" s="3"/>
     </row>
-    <row r="14" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
@@ -771,7 +790,7 @@
       <c r="K14" s="5"/>
       <c r="L14" s="5"/>
     </row>
-    <row r="15" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
@@ -784,7 +803,7 @@
       <c r="G15" s="3"/>
       <c r="H15" s="5"/>
     </row>
-    <row r="16" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
@@ -797,7 +816,7 @@
       <c r="G16" s="3"/>
       <c r="H16" s="5"/>
     </row>
-    <row r="17" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="2"/>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
@@ -810,7 +829,7 @@
       <c r="G17" s="3"/>
       <c r="H17" s="5"/>
     </row>
-    <row r="18" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
@@ -823,7 +842,7 @@
       <c r="G18" s="3"/>
       <c r="H18" s="3"/>
     </row>
-    <row r="19" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="2"/>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
@@ -833,7 +852,7 @@
       <c r="G19" s="3"/>
       <c r="H19" s="5"/>
     </row>
-    <row r="20" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="2"/>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
@@ -843,7 +862,7 @@
       <c r="G20" s="3"/>
       <c r="H20" s="5"/>
     </row>
-    <row r="21" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="2"/>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
@@ -853,7 +872,7 @@
       <c r="G21" s="3"/>
       <c r="H21" s="5"/>
     </row>
-    <row r="22" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
@@ -863,7 +882,7 @@
       <c r="G22" s="3"/>
       <c r="H22" s="5"/>
     </row>
-    <row r="23" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="2"/>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
@@ -873,7 +892,7 @@
       <c r="G23" s="3"/>
       <c r="H23" s="5"/>
     </row>
-    <row r="24" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
@@ -883,7 +902,7 @@
       <c r="G24" s="3"/>
       <c r="H24" s="5"/>
     </row>
-    <row r="25" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
@@ -893,7 +912,7 @@
       <c r="G25" s="3"/>
       <c r="H25" s="5"/>
     </row>
-    <row r="26" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
@@ -903,7 +922,7 @@
       <c r="G26" s="3"/>
       <c r="H26" s="3"/>
     </row>
-    <row r="27" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="2"/>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
@@ -913,7 +932,7 @@
       <c r="G27" s="3"/>
       <c r="H27" s="5"/>
     </row>
-    <row r="28" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
@@ -923,7 +942,7 @@
       <c r="G28" s="3"/>
       <c r="H28" s="5"/>
     </row>
-    <row r="29" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="2"/>
       <c r="B29" s="2"/>
       <c r="C29" s="2"/>
@@ -933,7 +952,7 @@
       <c r="G29" s="3"/>
       <c r="H29" s="5"/>
     </row>
-    <row r="30" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="2"/>
       <c r="B30" s="5"/>
       <c r="C30" s="2"/>
@@ -943,7 +962,7 @@
       <c r="G30" s="3"/>
       <c r="H30" s="3"/>
     </row>
-    <row r="31" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="2"/>
       <c r="B31" s="2"/>
       <c r="C31" s="2"/>
@@ -953,7 +972,7 @@
       <c r="G31" s="3"/>
       <c r="H31" s="5"/>
     </row>
-    <row r="32" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="2"/>
       <c r="B32" s="2"/>
       <c r="C32" s="2"/>
@@ -964,7 +983,7 @@
       <c r="H32" s="3"/>
       <c r="I32" s="5"/>
     </row>
-    <row r="33" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="2"/>
       <c r="B33" s="2"/>
       <c r="C33" s="2"/>
@@ -973,7 +992,7 @@
       <c r="F33" s="2"/>
       <c r="G33" s="8"/>
     </row>
-    <row r="34" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="2"/>
       <c r="B34" s="2"/>
       <c r="C34" s="2"/>
@@ -983,7 +1002,7 @@
       <c r="G34" s="3"/>
       <c r="H34" s="5"/>
     </row>
-    <row r="35" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="2"/>
       <c r="B35" s="5"/>
       <c r="C35" s="2"/>
@@ -993,7 +1012,7 @@
       <c r="G35" s="3"/>
       <c r="H35" s="5"/>
     </row>
-    <row r="36" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="2"/>
       <c r="B36" s="2"/>
       <c r="C36" s="2"/>
@@ -1003,7 +1022,7 @@
       <c r="G36" s="3"/>
       <c r="H36" s="5"/>
     </row>
-    <row r="37" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="2"/>
       <c r="B37" s="2"/>
       <c r="C37" s="2"/>
@@ -1012,7 +1031,7 @@
       <c r="F37" s="6"/>
       <c r="G37" s="3"/>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" s="2"/>
       <c r="B38" s="2"/>
       <c r="C38" s="2"/>
@@ -1021,7 +1040,7 @@
       <c r="F38" s="6"/>
       <c r="G38" s="1"/>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" s="2"/>
       <c r="B39" s="2"/>
       <c r="C39" s="2"/>
@@ -1030,7 +1049,7 @@
       <c r="F39" s="2"/>
       <c r="G39" s="8"/>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" s="2"/>
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
@@ -1039,14 +1058,14 @@
       <c r="F40" s="2"/>
       <c r="G40" s="1"/>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" s="2"/>
       <c r="B41" s="2"/>
       <c r="C41" s="2"/>
       <c r="D41" s="2"/>
       <c r="G41" s="1"/>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" s="2"/>
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
@@ -1055,21 +1074,22 @@
       <c r="F42" s="6"/>
       <c r="G42" s="1"/>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="D43" s="7" t="s">
         <v>11</v>
       </c>
       <c r="E43" s="6">
         <f>SUM(E3:E42)</f>
-        <v>3.88</v>
+        <v>51.080000000000005</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="G3" r:id="rId1" xr:uid="{7CE8A9C6-08F5-40BF-BA7F-EC621D56129B}"/>
     <hyperlink ref="G5" r:id="rId2" xr:uid="{7BE5D66A-4309-4B5F-B4A1-BE563118891A}"/>
+    <hyperlink ref="G4" r:id="rId3" display="https://www.grainger.com/product/1PZD5?gucid=N:N:FPL:Free:MS:CSM-1946:tew63h4:20501231&amp;gucid=N:N:PS:Paid:GGL:CSM-2295:UU5CX9:20800606:APZ_1&amp;gclsrc=aw.ds&amp;gad_source=1&amp;gad_campaignid=22475795893&amp;gclid=Cj0KCQiAgvPKBhCxARIsAOlK_EpGTxCUrLLeHl2B2PDU9Qyz8Ndfo0lyhe-JfENwhXPI-CsP3xbN6h8aAu77EALw_wcB" xr:uid="{59DCA364-B812-492A-AE20-B1FAFEF9ADBB}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId3"/>
+  <pageSetup orientation="portrait" r:id="rId4"/>
 </worksheet>
 </file>
--- a/resources/design_documents/BOM-thermal-loop.xlsx
+++ b/resources/design_documents/BOM-thermal-loop.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/94ce74fd9ae883e9/Documents/GitHub/thermal-loop/resources/design_documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="13_ncr:1_{80E5F55D-10A6-42B5-AE9E-C0AB2EBC7ED2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E9AC8987-F238-4932-88EE-4BEB160FD40B}"/>
+  <xr:revisionPtr revIDLastSave="29" documentId="13_ncr:1_{80E5F55D-10A6-42B5-AE9E-C0AB2EBC7ED2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0DDD1C4A-403B-4D08-A066-50ED029A4896}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{FDAE7DA4-9528-4FC7-A320-70DA50473DCE}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
   <si>
     <t>Total Cost</t>
   </si>
@@ -77,12 +77,6 @@
     <t xml:space="preserve">Notes </t>
   </si>
   <si>
-    <t>https://www.grainger.com/product/1MKB7?gucid=N:N:PS:Paid:GGL:CSM-2295:ZRUQJH:20800606:APZ_1&amp;gclsrc=aw.ds&amp;gad_source=4&amp;gad_campaignid=22472343581&amp;gclid=CjwKCAiA3-3KBhBiEiwA2x7FdMbC-r7MRiVr7w70QY_m83YfUZOkHFETUemE48AeCoPwtwXNXI1CgxoCD1UQAvD_BwE</t>
-  </si>
-  <si>
-    <t>Pipe Straight: Bushing, 1 in x 1/2 in Fitting Pipe Size, Schedule 80, Male NPT x Female NPT, Black</t>
-  </si>
-  <si>
     <t>rod top seal flange</t>
   </si>
   <si>
@@ -92,28 +86,43 @@
     <t>rod top seal compression ring</t>
   </si>
   <si>
-    <t>https://midwestsupplyus.com/products/crown-r83118-36?srsltid=AfmBOoqQzhZR4Lpivuxz8JACIO7F-PxUojc1qD-4FdncL46Gm-cpf9BiUB8</t>
-  </si>
-  <si>
     <t>heated rod</t>
   </si>
   <si>
-    <t>R83118-36 | NICHROME ROD .125 OD X 36" L | Crown Engineering</t>
-  </si>
-  <si>
-    <t>Pipe Flange: Floor Flange, 304 Stainless Steel, 1 in Pipe Size, 4 1/4 in Flange Outside Diameter</t>
-  </si>
-  <si>
     <t>Needed Larger Flange, but can downsize if needed</t>
   </si>
   <si>
-    <t>https://www.grainger.com/product/Pipe-Flange-Floor-Flange-4WPU8</t>
-  </si>
-  <si>
-    <t>PARKER Compression Fitting Adapter: 3/8 in OD x 1/2 in Pipe Fitting Size, Compression x MNPT</t>
-  </si>
-  <si>
-    <t>https://www.grainger.com/product/1PZD5?gucid=N:N:FPL:Free:MS:CSM-1946:tew63h4:20501231&amp;gucid=N:N:PS:Paid:GGL:CSM-2295:UU5CX9:20800606:APZ_1&amp;gclsrc=aw.ds&amp;gad_source=1&amp;gad_campaignid=22475795893&amp;gclid=Cj0KCQiAgvPKBhCxARIsAOlK_EpGTxCUrLLeHl2B2PDU9Qyz8Ndfo0lyhe-JfENwhXPI-CsP3xbN6h8aAu77EALw_wcB</t>
+    <t>Pipe Straight: Bushing, 1 1/2 in x 3/4 in Fitting Pipe Size, Schedule 80, Male NPT x Female NPT</t>
+  </si>
+  <si>
+    <t>https://www.grainger.com/product/1MKC2?gucid=N:N:FPL:Free:MS:CSM-1946:tew63h4:20501231&amp;gucid=N:N:PS:Paid:GGL:CSM-2295:ZRUQJH:20800606:APZ_1&amp;gclsrc=aw.ds&amp;gad_source=4&amp;gad_campaignid=22472343581&amp;gclid=Cj0KCQiAyP3KBhD9ARIsAAJLnnZV3FrrMMW30hmQUU1G4R6t9R910azLkt4b0E5gRseHoTUa98qjbrAaAtruEALw_wcB</t>
+  </si>
+  <si>
+    <t>APPROVED VENDOR Pipe Flange: Steel, Threaded Flange, 1 1/2 in Pipe Size, Raised Face Threaded Flange</t>
+  </si>
+  <si>
+    <t>https://www.grainger.com/product/4TXF5?gucid=N:N:FPL:Free:GGL:CSM-1946:tew63h3:20501231</t>
+  </si>
+  <si>
+    <t>PARKER Compression Fitting Adapter: 1/2 in OD x 3/4 in Pipe Fitting Size, Compression x MNPT</t>
+  </si>
+  <si>
+    <t>https://www.grainger.com/product/2KKX5?gucid=N:N:PS:Paid:GGL:CSM-2295:UU5CX9:20800606:APZ_1&amp;gclsrc=aw.ds&amp;gad_source=1&amp;gad_campaignid=22475795893&amp;gclid=Cj0KCQiAyP3KBhD9ARIsAAJLnnaI2Hs8ee39Gi-kgivmDRybdXzY3qDvMaoXfb5nBBu7KnfStFkr050aAiZREALw_wcB</t>
+  </si>
+  <si>
+    <t>NICHROME ROD Various lengths, OD 1/2 in (12.7 mm)</t>
+  </si>
+  <si>
+    <t>Price Varies</t>
+  </si>
+  <si>
+    <t>https://www.alibaba.com/product-detail/Manufacture-High-Temperature-Nichrome-Nickel-Alloy_1600301871567.html?spm=a2700.prosearch.normal_offer.d_title.936367afbZjywP&amp;priceId=7971a51af016405b9b2af3bda7ecc84f</t>
+  </si>
+  <si>
+    <t>https://www.alibaba.com/product-detail/Nichrome-Round-Circle-Rod-Inconel-713_1601578632529.html?spm=a2700.prosearch.normal_offer.d_title.326567afkT0hVH&amp;priceId=7d6d2e1736f541b98105b66ff059c288</t>
+  </si>
+  <si>
+    <t>https://www.alibaba.com/product-detail/Resistance-Nichrome-Alloy-Nicr-80-20_1601612829928.html?spm=a2700.prosearch.normal_offer.d_title.936367afbZjywP&amp;priceId=7971a51af016405b9b2af3bda7ecc84f</t>
   </si>
 </sst>
 </file>
@@ -201,6 +210,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -576,96 +589,106 @@
     </row>
     <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C2" s="2">
         <v>1</v>
       </c>
       <c r="D2" s="6">
-        <v>61.71</v>
+        <v>51.95</v>
       </c>
       <c r="E2" s="6">
         <f>C2*D2</f>
-        <v>61.71</v>
+        <v>51.95</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="H2" s="4"/>
       <c r="I2" s="4"/>
     </row>
     <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C3" s="2">
         <v>1</v>
       </c>
       <c r="D3" s="6">
-        <v>3.88</v>
+        <v>5.99</v>
       </c>
       <c r="E3" s="6">
         <f t="shared" ref="E3:E18" si="0">C3*D3</f>
-        <v>3.88</v>
+        <v>5.99</v>
       </c>
       <c r="F3" s="6"/>
       <c r="G3" s="3" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="H3" s="4"/>
     </row>
     <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C4" s="2">
         <v>1</v>
       </c>
       <c r="D4" s="6">
-        <v>47.2</v>
+        <v>81.94</v>
       </c>
       <c r="E4" s="6">
         <f t="shared" si="0"/>
-        <v>47.2</v>
+        <v>81.94</v>
       </c>
       <c r="F4" s="6"/>
       <c r="G4" s="3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="H4" s="5"/>
       <c r="I4" s="5"/>
     </row>
     <row r="5" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C5" s="2"/>
-      <c r="D5" s="6"/>
+        <v>24</v>
+      </c>
+      <c r="C5" s="2">
+        <v>1</v>
+      </c>
+      <c r="D5" s="6">
+        <v>0</v>
+      </c>
       <c r="E5" s="6">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F5" s="6"/>
+      <c r="F5" s="6" t="s">
+        <v>25</v>
+      </c>
       <c r="G5" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="H5" s="3"/>
-      <c r="I5" s="2"/>
+        <v>26</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="6" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2"/>
@@ -1080,16 +1103,11 @@
       </c>
       <c r="E43" s="6">
         <f>SUM(E3:E42)</f>
-        <v>51.080000000000005</v>
+        <v>87.929999999999993</v>
       </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="G3" r:id="rId1" xr:uid="{7CE8A9C6-08F5-40BF-BA7F-EC621D56129B}"/>
-    <hyperlink ref="G5" r:id="rId2" xr:uid="{7BE5D66A-4309-4B5F-B4A1-BE563118891A}"/>
-    <hyperlink ref="G4" r:id="rId3" display="https://www.grainger.com/product/1PZD5?gucid=N:N:FPL:Free:MS:CSM-1946:tew63h4:20501231&amp;gucid=N:N:PS:Paid:GGL:CSM-2295:UU5CX9:20800606:APZ_1&amp;gclsrc=aw.ds&amp;gad_source=1&amp;gad_campaignid=22475795893&amp;gclid=Cj0KCQiAgvPKBhCxARIsAOlK_EpGTxCUrLLeHl2B2PDU9Qyz8Ndfo0lyhe-JfENwhXPI-CsP3xbN6h8aAu77EALw_wcB" xr:uid="{59DCA364-B812-492A-AE20-B1FAFEF9ADBB}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId4"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/resources/design_documents/BOM-thermal-loop.xlsx
+++ b/resources/design_documents/BOM-thermal-loop.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29704"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/94ce74fd9ae883e9/Documents/GitHub/thermal-loop/resources/design_documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="29" documentId="13_ncr:1_{80E5F55D-10A6-42B5-AE9E-C0AB2EBC7ED2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0DDD1C4A-403B-4D08-A066-50ED029A4896}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F6A0CB86-34E3-4676-9B6A-89D84CAB0162}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{FDAE7DA4-9528-4FC7-A320-70DA50473DCE}"/>
   </bookViews>
   <sheets>
     <sheet name="bill_of_materials" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,21 +36,24 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="41">
+  <si>
+    <t>Designator</t>
+  </si>
+  <si>
+    <t>Component</t>
+  </si>
+  <si>
+    <t>Amount</t>
+  </si>
+  <si>
+    <t>Individual Cost</t>
+  </si>
   <si>
     <t>Total Cost</t>
   </si>
   <si>
-    <t>Designator</t>
-  </si>
-  <si>
-    <t>Component</t>
-  </si>
-  <si>
-    <t>Amount</t>
-  </si>
-  <si>
-    <t>Individual Cost</t>
+    <t xml:space="preserve">Notes </t>
   </si>
   <si>
     <t>Vendor 1</t>
@@ -71,58 +74,91 @@
     <t>Vendor 6</t>
   </si>
   <si>
+    <t>rod top seal flange</t>
+  </si>
+  <si>
+    <t>APPROVED VENDOR Pipe Flange: Steel, Threaded Flange, 1 1/2 in Pipe Size, Raised Face Threaded Flange</t>
+  </si>
+  <si>
+    <t>Needed Larger Flange, but can downsize if needed</t>
+  </si>
+  <si>
+    <t>https://www.grainger.com/product/4TXF5?gucid=N:N:FPL:Free:GGL:CSM-1946:tew63h3:20501231</t>
+  </si>
+  <si>
+    <t>rod top seal bushing</t>
+  </si>
+  <si>
+    <t>Pipe Straight: Bushing, 1 1/2 in x 3/4 in Fitting Pipe Size, Schedule 80, Male NPT x Female NPT</t>
+  </si>
+  <si>
+    <t>https://www.grainger.com/product/1MKC2?gucid=N:N:FPL:Free:MS:CSM-1946:tew63h4:20501231&amp;gucid=N:N:PS:Paid:GGL:CSM-2295:ZRUQJH:20800606:APZ_1&amp;gclsrc=aw.ds&amp;gad_source=4&amp;gad_campaignid=22472343581&amp;gclid=Cj0KCQiAyP3KBhD9ARIsAAJLnnZV3FrrMMW30hmQUU1G4R6t9R910azLkt4b0E5gRseHoTUa98qjbrAaAtruEALw_wcB</t>
+  </si>
+  <si>
+    <t>rod top seal compression ring</t>
+  </si>
+  <si>
+    <t>PARKER Compression Fitting Adapter: 1/2 in OD x 3/4 in Pipe Fitting Size, Compression x MNPT</t>
+  </si>
+  <si>
+    <t>https://www.grainger.com/product/2KKX5?gucid=N:N:PS:Paid:GGL:CSM-2295:UU5CX9:20800606:APZ_1&amp;gclsrc=aw.ds&amp;gad_source=1&amp;gad_campaignid=22475795893&amp;gclid=Cj0KCQiAyP3KBhD9ARIsAAJLnnaI2Hs8ee39Gi-kgivmDRybdXzY3qDvMaoXfb5nBBu7KnfStFkr050aAiZREALw_wcB</t>
+  </si>
+  <si>
+    <t>heated rod</t>
+  </si>
+  <si>
+    <t>NICHROME ROD Various lengths, OD 1/2 in (12.7 mm)</t>
+  </si>
+  <si>
+    <t>Price Varies</t>
+  </si>
+  <si>
+    <t>https://www.alibaba.com/product-detail/Manufacture-High-Temperature-Nichrome-Nickel-Alloy_1600301871567.html?spm=a2700.prosearch.normal_offer.d_title.936367afbZjywP&amp;priceId=7971a51af016405b9b2af3bda7ecc84f</t>
+  </si>
+  <si>
+    <t>https://www.alibaba.com/product-detail/Nichrome-Round-Circle-Rod-Inconel-713_1601578632529.html?spm=a2700.prosearch.normal_offer.d_title.326567afkT0hVH&amp;priceId=7d6d2e1736f541b98105b66ff059c288</t>
+  </si>
+  <si>
+    <t>https://www.alibaba.com/product-detail/Resistance-Nichrome-Alloy-Nicr-80-20_1601612829928.html?spm=a2700.prosearch.normal_offer.d_title.936367afbZjywP&amp;priceId=7971a51af016405b9b2af3bda7ecc84f</t>
+  </si>
+  <si>
+    <t>Control for Proportional Valve</t>
+  </si>
+  <si>
+    <t>Dig. control electroncis for prop.valves: 12-24 V/ 40-220 mA/ (-)10-60 C/ 80-6000 Hz. Article No. 316531</t>
+  </si>
+  <si>
+    <t>Ordered</t>
+  </si>
+  <si>
+    <t>https://www.burkert.com/en/products/solenoid-control-valves/controllers/316531</t>
+  </si>
+  <si>
+    <t>Power supply connector</t>
+  </si>
+  <si>
+    <t xml:space="preserve">plug A standard with UL: 0-250 V/ 10 A/ (-)30-90 C. Article No. 314802 </t>
+  </si>
+  <si>
+    <t>plug A standard with UL</t>
+  </si>
+  <si>
+    <t>Proportional Valve</t>
+  </si>
+  <si>
+    <t>2/2-way-proportional valve: normally closed/ 10 mm/ FKM / Brass / NPT inner thread / 24 V/ (-1)-3 bar/ (-)10-90 C. Article No. 164598</t>
+  </si>
+  <si>
+    <t>2/2-way-proportional valve</t>
+  </si>
+  <si>
+    <t>Dig. control electroncis for prop.valves: Calbe feed-through/ 12-24 V/ 200 - 1000 mA/ (-)10-60 C/ 80-6000 Hz</t>
+  </si>
+  <si>
+    <t>Dig. control electroncis for prop.valves</t>
+  </si>
+  <si>
     <t>Total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Notes </t>
-  </si>
-  <si>
-    <t>rod top seal flange</t>
-  </si>
-  <si>
-    <t>rod top seal bushing</t>
-  </si>
-  <si>
-    <t>rod top seal compression ring</t>
-  </si>
-  <si>
-    <t>heated rod</t>
-  </si>
-  <si>
-    <t>Needed Larger Flange, but can downsize if needed</t>
-  </si>
-  <si>
-    <t>Pipe Straight: Bushing, 1 1/2 in x 3/4 in Fitting Pipe Size, Schedule 80, Male NPT x Female NPT</t>
-  </si>
-  <si>
-    <t>https://www.grainger.com/product/1MKC2?gucid=N:N:FPL:Free:MS:CSM-1946:tew63h4:20501231&amp;gucid=N:N:PS:Paid:GGL:CSM-2295:ZRUQJH:20800606:APZ_1&amp;gclsrc=aw.ds&amp;gad_source=4&amp;gad_campaignid=22472343581&amp;gclid=Cj0KCQiAyP3KBhD9ARIsAAJLnnZV3FrrMMW30hmQUU1G4R6t9R910azLkt4b0E5gRseHoTUa98qjbrAaAtruEALw_wcB</t>
-  </si>
-  <si>
-    <t>APPROVED VENDOR Pipe Flange: Steel, Threaded Flange, 1 1/2 in Pipe Size, Raised Face Threaded Flange</t>
-  </si>
-  <si>
-    <t>https://www.grainger.com/product/4TXF5?gucid=N:N:FPL:Free:GGL:CSM-1946:tew63h3:20501231</t>
-  </si>
-  <si>
-    <t>PARKER Compression Fitting Adapter: 1/2 in OD x 3/4 in Pipe Fitting Size, Compression x MNPT</t>
-  </si>
-  <si>
-    <t>https://www.grainger.com/product/2KKX5?gucid=N:N:PS:Paid:GGL:CSM-2295:UU5CX9:20800606:APZ_1&amp;gclsrc=aw.ds&amp;gad_source=1&amp;gad_campaignid=22475795893&amp;gclid=Cj0KCQiAyP3KBhD9ARIsAAJLnnaI2Hs8ee39Gi-kgivmDRybdXzY3qDvMaoXfb5nBBu7KnfStFkr050aAiZREALw_wcB</t>
-  </si>
-  <si>
-    <t>NICHROME ROD Various lengths, OD 1/2 in (12.7 mm)</t>
-  </si>
-  <si>
-    <t>Price Varies</t>
-  </si>
-  <si>
-    <t>https://www.alibaba.com/product-detail/Manufacture-High-Temperature-Nichrome-Nickel-Alloy_1600301871567.html?spm=a2700.prosearch.normal_offer.d_title.936367afbZjywP&amp;priceId=7971a51af016405b9b2af3bda7ecc84f</t>
-  </si>
-  <si>
-    <t>https://www.alibaba.com/product-detail/Nichrome-Round-Circle-Rod-Inconel-713_1601578632529.html?spm=a2700.prosearch.normal_offer.d_title.326567afkT0hVH&amp;priceId=7d6d2e1736f541b98105b66ff059c288</t>
-  </si>
-  <si>
-    <t>https://www.alibaba.com/product-detail/Resistance-Nichrome-Alloy-Nicr-80-20_1601612829928.html?spm=a2700.prosearch.normal_offer.d_title.936367afbZjywP&amp;priceId=7971a51af016405b9b2af3bda7ecc84f</t>
   </si>
 </sst>
 </file>
@@ -132,7 +168,7 @@
   <numFmts count="1">
     <numFmt numFmtId="7" formatCode="&quot;$&quot;#,##0.00_);\(&quot;$&quot;#,##0.00\)"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -210,10 +246,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -534,65 +566,65 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6D3A36C-E8CE-4E50-A172-E48E2F9A45A8}">
   <dimension ref="A1:L43"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="25.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="25.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="74" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.5546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="12.33203125" customWidth="1"/>
-    <col min="7" max="7" width="69.44140625" customWidth="1"/>
+    <col min="3" max="3" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="12.28515625" customWidth="1"/>
+    <col min="7" max="7" width="69.42578125" customWidth="1"/>
     <col min="8" max="8" width="76" customWidth="1"/>
-    <col min="9" max="9" width="83.5546875" customWidth="1"/>
-    <col min="10" max="10" width="62.5546875" customWidth="1"/>
-    <col min="11" max="11" width="55.88671875" customWidth="1"/>
+    <col min="9" max="9" width="83.5703125" customWidth="1"/>
+    <col min="10" max="10" width="62.5703125" customWidth="1"/>
+    <col min="11" max="11" width="55.85546875" customWidth="1"/>
     <col min="12" max="12" width="51" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" ht="15" customHeight="1">
       <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="2" t="s">
-        <v>0</v>
-      </c>
       <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" ht="15" customHeight="1">
+      <c r="A2" t="s">
         <v>12</v>
       </c>
-      <c r="G1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="B2" s="2" t="s">
         <v>13</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>20</v>
       </c>
       <c r="C2" s="2">
         <v>1</v>
@@ -605,20 +637,20 @@
         <v>51.95</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="H2" s="4"/>
       <c r="I2" s="4"/>
     </row>
-    <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" ht="15" customHeight="1">
       <c r="A3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C3" s="2">
         <v>1</v>
@@ -632,16 +664,16 @@
       </c>
       <c r="F3" s="6"/>
       <c r="G3" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H3" s="4"/>
+    </row>
+    <row r="4" spans="1:12" ht="15" customHeight="1">
+      <c r="A4" t="s">
         <v>19</v>
       </c>
-      <c r="H3" s="4"/>
-    </row>
-    <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>15</v>
-      </c>
       <c r="B4" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C4" s="2">
         <v>1</v>
@@ -655,17 +687,17 @@
       </c>
       <c r="F4" s="6"/>
       <c r="G4" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="H4" s="5"/>
       <c r="I4" s="5"/>
     </row>
-    <row r="5" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" ht="15" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C5" s="2">
         <v>1</v>
@@ -678,73 +710,121 @@
         <v>0</v>
       </c>
       <c r="F5" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="G5" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="H5" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="H5" s="3" t="s">
+      <c r="I5" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="I5" s="2" t="s">
+    </row>
+    <row r="6" spans="1:12" ht="15" customHeight="1">
+      <c r="A6" s="2" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="6" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="2"/>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="6"/>
+      <c r="B6" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6" s="2">
+        <v>1</v>
+      </c>
+      <c r="D6" s="6">
+        <v>370</v>
+      </c>
       <c r="E6" s="6">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F6" s="6"/>
-      <c r="G6" s="3"/>
+        <v>370</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="H6" s="3"/>
       <c r="I6" s="3"/>
     </row>
-    <row r="7" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="2"/>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="6"/>
+    <row r="7" spans="1:12" ht="15" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C7" s="2">
+        <v>1</v>
+      </c>
+      <c r="D7" s="6">
+        <v>5.9</v>
+      </c>
       <c r="E7" s="6">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F7" s="6"/>
-      <c r="G7" s="3"/>
+        <v>5.9</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>34</v>
+      </c>
       <c r="H7" s="3"/>
       <c r="I7" s="2"/>
     </row>
-    <row r="8" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="2"/>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="6"/>
+    <row r="8" spans="1:12" ht="15" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C8" s="2">
+        <v>1</v>
+      </c>
+      <c r="D8" s="6">
+        <v>1610</v>
+      </c>
       <c r="E8" s="6">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F8" s="6"/>
-      <c r="G8" s="3"/>
-    </row>
-    <row r="9" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="2"/>
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="6"/>
+        <v>1610</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="15" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C9" s="2">
+        <v>1</v>
+      </c>
+      <c r="D9" s="6">
+        <v>405</v>
+      </c>
       <c r="E9" s="6">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F9" s="6"/>
-      <c r="G9" s="3"/>
+        <v>405</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>39</v>
+      </c>
       <c r="H9" s="5"/>
       <c r="I9" s="5"/>
     </row>
-    <row r="10" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" ht="15" customHeight="1">
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
@@ -758,7 +838,7 @@
       <c r="H10" s="3"/>
       <c r="I10" s="5"/>
     </row>
-    <row r="11" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" ht="15" customHeight="1">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
@@ -771,7 +851,7 @@
       <c r="G11" s="3"/>
       <c r="H11" s="5"/>
     </row>
-    <row r="12" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" ht="15" customHeight="1">
       <c r="A12" s="2"/>
       <c r="B12" s="5"/>
       <c r="C12" s="2"/>
@@ -784,7 +864,7 @@
       <c r="G12" s="3"/>
       <c r="H12" s="5"/>
     </row>
-    <row r="13" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" ht="15" customHeight="1">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
@@ -796,7 +876,7 @@
       <c r="F13" s="6"/>
       <c r="G13" s="3"/>
     </row>
-    <row r="14" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" ht="15" customHeight="1">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
@@ -813,7 +893,7 @@
       <c r="K14" s="5"/>
       <c r="L14" s="5"/>
     </row>
-    <row r="15" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" ht="15" customHeight="1">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
@@ -826,7 +906,7 @@
       <c r="G15" s="3"/>
       <c r="H15" s="5"/>
     </row>
-    <row r="16" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" ht="15" customHeight="1">
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
@@ -839,7 +919,7 @@
       <c r="G16" s="3"/>
       <c r="H16" s="5"/>
     </row>
-    <row r="17" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" ht="15" customHeight="1">
       <c r="A17" s="2"/>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
@@ -852,7 +932,7 @@
       <c r="G17" s="3"/>
       <c r="H17" s="5"/>
     </row>
-    <row r="18" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" ht="15" customHeight="1">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
@@ -865,7 +945,7 @@
       <c r="G18" s="3"/>
       <c r="H18" s="3"/>
     </row>
-    <row r="19" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" ht="15" customHeight="1">
       <c r="A19" s="2"/>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
@@ -875,7 +955,7 @@
       <c r="G19" s="3"/>
       <c r="H19" s="5"/>
     </row>
-    <row r="20" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9" ht="15" customHeight="1">
       <c r="A20" s="2"/>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
@@ -885,7 +965,7 @@
       <c r="G20" s="3"/>
       <c r="H20" s="5"/>
     </row>
-    <row r="21" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9" ht="15" customHeight="1">
       <c r="A21" s="2"/>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
@@ -895,7 +975,7 @@
       <c r="G21" s="3"/>
       <c r="H21" s="5"/>
     </row>
-    <row r="22" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9" ht="15" customHeight="1">
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
@@ -905,7 +985,7 @@
       <c r="G22" s="3"/>
       <c r="H22" s="5"/>
     </row>
-    <row r="23" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:9" ht="15" customHeight="1">
       <c r="A23" s="2"/>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
@@ -915,7 +995,7 @@
       <c r="G23" s="3"/>
       <c r="H23" s="5"/>
     </row>
-    <row r="24" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:9" ht="15" customHeight="1">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
@@ -925,7 +1005,7 @@
       <c r="G24" s="3"/>
       <c r="H24" s="5"/>
     </row>
-    <row r="25" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:9" ht="15" customHeight="1">
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
@@ -935,7 +1015,7 @@
       <c r="G25" s="3"/>
       <c r="H25" s="5"/>
     </row>
-    <row r="26" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:9" ht="15" customHeight="1">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
@@ -945,7 +1025,7 @@
       <c r="G26" s="3"/>
       <c r="H26" s="3"/>
     </row>
-    <row r="27" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:9" ht="15" customHeight="1">
       <c r="A27" s="2"/>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
@@ -955,7 +1035,7 @@
       <c r="G27" s="3"/>
       <c r="H27" s="5"/>
     </row>
-    <row r="28" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:9" ht="15" customHeight="1">
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
@@ -965,7 +1045,7 @@
       <c r="G28" s="3"/>
       <c r="H28" s="5"/>
     </row>
-    <row r="29" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:9" ht="15" customHeight="1">
       <c r="A29" s="2"/>
       <c r="B29" s="2"/>
       <c r="C29" s="2"/>
@@ -975,7 +1055,7 @@
       <c r="G29" s="3"/>
       <c r="H29" s="5"/>
     </row>
-    <row r="30" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:9" ht="15" customHeight="1">
       <c r="A30" s="2"/>
       <c r="B30" s="5"/>
       <c r="C30" s="2"/>
@@ -985,7 +1065,7 @@
       <c r="G30" s="3"/>
       <c r="H30" s="3"/>
     </row>
-    <row r="31" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:9" ht="15" customHeight="1">
       <c r="A31" s="2"/>
       <c r="B31" s="2"/>
       <c r="C31" s="2"/>
@@ -995,7 +1075,7 @@
       <c r="G31" s="3"/>
       <c r="H31" s="5"/>
     </row>
-    <row r="32" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:9" ht="15" customHeight="1">
       <c r="A32" s="2"/>
       <c r="B32" s="2"/>
       <c r="C32" s="2"/>
@@ -1006,7 +1086,7 @@
       <c r="H32" s="3"/>
       <c r="I32" s="5"/>
     </row>
-    <row r="33" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:8" ht="15" customHeight="1">
       <c r="A33" s="2"/>
       <c r="B33" s="2"/>
       <c r="C33" s="2"/>
@@ -1015,7 +1095,7 @@
       <c r="F33" s="2"/>
       <c r="G33" s="8"/>
     </row>
-    <row r="34" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:8" ht="15" customHeight="1">
       <c r="A34" s="2"/>
       <c r="B34" s="2"/>
       <c r="C34" s="2"/>
@@ -1025,7 +1105,7 @@
       <c r="G34" s="3"/>
       <c r="H34" s="5"/>
     </row>
-    <row r="35" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:8" ht="15" customHeight="1">
       <c r="A35" s="2"/>
       <c r="B35" s="5"/>
       <c r="C35" s="2"/>
@@ -1035,7 +1115,7 @@
       <c r="G35" s="3"/>
       <c r="H35" s="5"/>
     </row>
-    <row r="36" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:8" ht="15" customHeight="1">
       <c r="A36" s="2"/>
       <c r="B36" s="2"/>
       <c r="C36" s="2"/>
@@ -1045,7 +1125,7 @@
       <c r="G36" s="3"/>
       <c r="H36" s="5"/>
     </row>
-    <row r="37" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:8" ht="15" customHeight="1">
       <c r="A37" s="2"/>
       <c r="B37" s="2"/>
       <c r="C37" s="2"/>
@@ -1054,7 +1134,7 @@
       <c r="F37" s="6"/>
       <c r="G37" s="3"/>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:8">
       <c r="A38" s="2"/>
       <c r="B38" s="2"/>
       <c r="C38" s="2"/>
@@ -1063,7 +1143,7 @@
       <c r="F38" s="6"/>
       <c r="G38" s="1"/>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:8">
       <c r="A39" s="2"/>
       <c r="B39" s="2"/>
       <c r="C39" s="2"/>
@@ -1072,7 +1152,7 @@
       <c r="F39" s="2"/>
       <c r="G39" s="8"/>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:8">
       <c r="A40" s="2"/>
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
@@ -1081,14 +1161,14 @@
       <c r="F40" s="2"/>
       <c r="G40" s="1"/>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:8">
       <c r="A41" s="2"/>
       <c r="B41" s="2"/>
       <c r="C41" s="2"/>
       <c r="D41" s="2"/>
       <c r="G41" s="1"/>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:8">
       <c r="A42" s="2"/>
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
@@ -1097,17 +1177,23 @@
       <c r="F42" s="6"/>
       <c r="G42" s="1"/>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:8">
       <c r="D43" s="7" t="s">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="E43" s="6">
         <f>SUM(E3:E42)</f>
-        <v>87.929999999999993</v>
+        <v>2478.83</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="G6" r:id="rId1" xr:uid="{E33C014D-D38A-4F5C-8E68-C4A037C95327}"/>
+    <hyperlink ref="G7" r:id="rId2" xr:uid="{DEDB84EA-1F93-4E7A-B728-715B3699A617}"/>
+    <hyperlink ref="G8" r:id="rId3" xr:uid="{2B7851C3-B223-4CA7-B169-6247D278EB5E}"/>
+    <hyperlink ref="G9" r:id="rId4" xr:uid="{8AE81AC0-6063-4F93-9808-8CC77409A5DB}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId5"/>
 </worksheet>
 </file>
--- a/resources/design_documents/BOM-thermal-loop.xlsx
+++ b/resources/design_documents/BOM-thermal-loop.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/94ce74fd9ae883e9/Documents/GitHub/thermal-loop/resources/design_documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="29" documentId="13_ncr:1_{80E5F55D-10A6-42B5-AE9E-C0AB2EBC7ED2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0DDD1C4A-403B-4D08-A066-50ED029A4896}"/>
+  <xr:revisionPtr revIDLastSave="41" documentId="13_ncr:1_{80E5F55D-10A6-42B5-AE9E-C0AB2EBC7ED2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CE98D366-C31A-4567-B77B-F732C8CE2F94}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{FDAE7DA4-9528-4FC7-A320-70DA50473DCE}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
   <si>
     <t>Total Cost</t>
   </si>
@@ -123,6 +123,18 @@
   </si>
   <si>
     <t>https://www.alibaba.com/product-detail/Resistance-Nichrome-Alloy-Nicr-80-20_1601612829928.html?spm=a2700.prosearch.normal_offer.d_title.936367afbZjywP&amp;priceId=7971a51af016405b9b2af3bda7ecc84f</t>
+  </si>
+  <si>
+    <t>Gray Cable</t>
+  </si>
+  <si>
+    <t>4 (2 Pair) Conductor Multi-Pair Cable Gray 28 AWG Foil, Braid Enter Number of Feet in Order Quantity</t>
+  </si>
+  <si>
+    <t>Price Per Foot</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/belden-inc/76402TS-0081000/8121749?gclsrc=aw.ds&amp;gad_source=1&amp;gad_campaignid=17336967819&amp;gbraid=0AAAAADrbLliFYeEY1zGYMTweHRoLgpUiC&amp;gclid=CjwKCAiAvaLLBhBFEiwAYCNTf474ZmceJINd-_V3kh0Y0U7TrBMEFaYTCsHI46C9SlD8tcFBGIDj-BoCIU0QAvD_BwE</t>
   </si>
 </sst>
 </file>
@@ -537,11 +549,11 @@
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="25.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="74" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="86.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.33203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12.5546875" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="12.33203125" customWidth="1"/>
-    <col min="7" max="7" width="69.44140625" customWidth="1"/>
+    <col min="7" max="7" width="255.77734375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="76" customWidth="1"/>
     <col min="9" max="9" width="83.5546875" customWidth="1"/>
     <col min="10" max="10" width="62.5546875" customWidth="1"/>
@@ -691,16 +703,28 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="2"/>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="6"/>
+      <c r="A6" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C6" s="2">
+        <v>25</v>
+      </c>
+      <c r="D6" s="6">
+        <v>3.97</v>
+      </c>
       <c r="E6" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F6" s="6"/>
-      <c r="G6" s="3"/>
+        <f>C6*D6</f>
+        <v>99.25</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>32</v>
+      </c>
       <c r="H6" s="3"/>
       <c r="I6" s="3"/>
     </row>
@@ -1103,7 +1127,7 @@
       </c>
       <c r="E43" s="6">
         <f>SUM(E3:E42)</f>
-        <v>87.929999999999993</v>
+        <v>187.18</v>
       </c>
     </row>
   </sheetData>
